--- a/data/google_forms_export.xlsx
+++ b/data/google_forms_export.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="114">
   <si>
     <t>Timestamp</t>
   </si>
@@ -230,12 +230,138 @@
   </si>
   <si>
     <t xml:space="preserve">Επιπλέον σχόλια ή προτάσεις. </t>
+  </si>
+  <si>
+    <t>ΠΑΔΑ</t>
+  </si>
+  <si>
+    <t>6 μηνες</t>
+  </si>
+  <si>
+    <t>Μαρτιος- Αυγουστος</t>
+  </si>
+  <si>
+    <t>1 Καθόλου</t>
+  </si>
+  <si>
+    <t>Δεν συμμετείχα</t>
+  </si>
+  <si>
+    <t>1 – Πολύ χαμηλή</t>
+  </si>
+  <si>
+    <t>1 – Καθόλου</t>
+  </si>
+  <si>
+    <t>Δεν υπηρχαν</t>
+  </si>
+  <si>
+    <t>Ολοι</t>
+  </si>
+  <si>
+    <t>Ολες</t>
+  </si>
+  <si>
+    <t>Πολλες</t>
+  </si>
+  <si>
+    <t>Δεν έχω. Κακή εμπειρία συνολικα</t>
+  </si>
+  <si>
+    <t>Χρειάζεται βελτιωση</t>
+  </si>
+  <si>
+    <t>Παδα</t>
+  </si>
+  <si>
+    <t>4ο</t>
+  </si>
+  <si>
+    <t>4 μηνες</t>
+  </si>
+  <si>
+    <t>20/3/2026 - 20/2026</t>
+  </si>
+  <si>
+    <t>Μέτρια</t>
+  </si>
+  <si>
+    <t>3 – Μέτρια</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Η συνεργασία </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Τουαλέτες </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Αναπνευστικές </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Σεμινάρια </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ρομποτικά </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Να μεγαλώσει το ωράριο </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 μήνες </t>
+  </si>
+  <si>
+    <t>20/3/2026 - 20/8/2026</t>
+  </si>
+  <si>
+    <t>5 Άριστα</t>
+  </si>
+  <si>
+    <t>Πολύ υψηλή</t>
+  </si>
+  <si>
+    <t>5 – Πολύ υψηλή</t>
+  </si>
+  <si>
+    <t>5 – Άριστα</t>
+  </si>
+  <si>
+    <t>Οαδα</t>
+  </si>
+  <si>
+    <t>20/4/2026 - 20/8/2026</t>
+  </si>
+  <si>
+    <t>Χαμηλή</t>
+  </si>
+  <si>
+    <t>Υψηλή</t>
+  </si>
+  <si>
+    <t>2 – Χαμηλή</t>
+  </si>
+  <si>
+    <t>4 – Υψηλή</t>
+  </si>
+  <si>
+    <t>2 – Λίγο</t>
+  </si>
+  <si>
+    <t>4 – Πολύ</t>
+  </si>
+  <si>
+    <t>Λαμια</t>
+  </si>
+  <si>
+    <t>Πολύ χαμηλή</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="10.0"/>
@@ -263,12 +389,24 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -349,88 +487,83 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:BU1" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:BU6" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="73">
-    <tableColumn name="Column1" id="1"/>
-    <tableColumn name="Column2" id="2"/>
-    <tableColumn name="Column3" id="3"/>
-    <tableColumn name="Column4" id="4"/>
-    <tableColumn name="Column5" id="5"/>
-    <tableColumn name="Column6" id="6"/>
-    <tableColumn name="Column7" id="7"/>
-    <tableColumn name="Column8" id="8"/>
-    <tableColumn name="Column9" id="9"/>
-    <tableColumn name="Column10" id="10"/>
-    <tableColumn name="Column11" id="11"/>
-    <tableColumn name="Column12" id="12"/>
-    <tableColumn name="Column13" id="13"/>
-    <tableColumn name="Column14" id="14"/>
-    <tableColumn name="Column15" id="15"/>
-    <tableColumn name="Column16" id="16"/>
-    <tableColumn name="Column17" id="17"/>
-    <tableColumn name="Column18" id="18"/>
-    <tableColumn name="Column19" id="19"/>
-    <tableColumn name="Column20" id="20"/>
-    <tableColumn name="Column21" id="21"/>
-    <tableColumn name="Column22" id="22"/>
-    <tableColumn name="Column23" id="23"/>
-    <tableColumn name="Column24" id="24"/>
-    <tableColumn name="Column25" id="25"/>
-    <tableColumn name="Column26" id="26"/>
-    <tableColumn name="Column27" id="27"/>
-    <tableColumn name="Column28" id="28"/>
-    <tableColumn name="Column29" id="29"/>
-    <tableColumn name="Column30" id="30"/>
-    <tableColumn name="Column31" id="31"/>
-    <tableColumn name="Column32" id="32"/>
-    <tableColumn name="Column33" id="33"/>
-    <tableColumn name="Column34" id="34"/>
-    <tableColumn name="Column35" id="35"/>
-    <tableColumn name="Column36" id="36"/>
-    <tableColumn name="Column37" id="37"/>
-    <tableColumn name="Column38" id="38"/>
-    <tableColumn name="Column39" id="39"/>
-    <tableColumn name="Column40" id="40"/>
-    <tableColumn name="Column41" id="41"/>
-    <tableColumn name="Column42" id="42"/>
-    <tableColumn name="Column43" id="43"/>
-    <tableColumn name="Column44" id="44"/>
-    <tableColumn name="Column45" id="45"/>
-    <tableColumn name="Column46" id="46"/>
-    <tableColumn name="Column47" id="47"/>
-    <tableColumn name="Column48" id="48"/>
-    <tableColumn name="Column49" id="49"/>
-    <tableColumn name="Column50" id="50"/>
-    <tableColumn name="Column51" id="51"/>
-    <tableColumn name="Column52" id="52"/>
-    <tableColumn name="Column53" id="53"/>
-    <tableColumn name="Column54" id="54"/>
-    <tableColumn name="Column55" id="55"/>
-    <tableColumn name="Column56" id="56"/>
-    <tableColumn name="Column57" id="57"/>
-    <tableColumn name="Column58" id="58"/>
-    <tableColumn name="Column59" id="59"/>
-    <tableColumn name="Column60" id="60"/>
-    <tableColumn name="Column61" id="61"/>
-    <tableColumn name="Column62" id="62"/>
-    <tableColumn name="Column63" id="63"/>
-    <tableColumn name="Column64" id="64"/>
-    <tableColumn name="Column65" id="65"/>
-    <tableColumn name="Column66" id="66"/>
-    <tableColumn name="Column67" id="67"/>
-    <tableColumn name="Column68" id="68"/>
-    <tableColumn name="Column69" id="69"/>
-    <tableColumn name="Column70" id="70"/>
-    <tableColumn name="Column71" id="71"/>
-    <tableColumn name="Column72" id="72"/>
-    <tableColumn name="Column73" id="73"/>
+    <tableColumn name="Timestamp" id="1"/>
+    <tableColumn name="Πανεπιστήμιο " id="2"/>
+    <tableColumn name="Έτος σπουδών " id="3"/>
+    <tableColumn name="Διάρκεια πρακτικής " id="4"/>
+    <tableColumn name="Περίοδος πρακτικής " id="5"/>
+    <tableColumn name=" [Υποδοχή]" id="6"/>
+    <tableColumn name=" [Ενημέρωση]" id="7"/>
+    <tableColumn name=" [Οργάνωση προγράμματος]" id="8"/>
+    <tableColumn name=" [Κατανομή περιστατικών]" id="9"/>
+    <tableColumn name=" [Συνέπεια προγράμματος]" id="10"/>
+    <tableColumn name=" [Διαθεσιμότητα υπευθύνων]" id="11"/>
+    <tableColumn name=" [Συνολική οργάνωση]" id="12"/>
+    <tableColumn name=" [Νευρολογική αποκατάσταση]" id="13"/>
+    <tableColumn name=" [Ορθοπαιδική αποκατάσταση]" id="14"/>
+    <tableColumn name=" [Γηριατρική αποκατάσταση]" id="15"/>
+    <tableColumn name=" [Ρομποτική αποκατάσταση]" id="16"/>
+    <tableColumn name=" [Θεραπευτική άσκηση]" id="17"/>
+    <tableColumn name=" [Υδροθεραπεία εντός πισίνας]" id="18"/>
+    <tableColumn name=" [Κρουστικά κύματα]" id="19"/>
+    <tableColumn name=" [Εκπαίδευση στη βάδιση]" id="20"/>
+    <tableColumn name=" [Αξιολόγηση ασθενών]" id="21"/>
+    <tableColumn name=" [Καταγραφή στον φάκελο ασθενούς]" id="22"/>
+    <tableColumn name=" [Παρουσίαση περιστατικών]" id="23"/>
+    <tableColumn name=" [Συμμετοχή στη διεπιστημονική ομάδα]" id="24"/>
+    <tableColumn name=" [Ανάπτυξη κλινικής σκέψης]" id="25"/>
+    <tableColumn name=" [Εφαρμογή επιστημονικής γνώσης]" id="26"/>
+    <tableColumn name=" [Ευκαιρίες πρακτικής εξάσκησης]" id="27"/>
+    <tableColumn name=" [Εποικοδομητική ανατροφοδότηση]" id="28"/>
+    <tableColumn name=" [Αυτονομία υπό επίβλεψη]" id="29"/>
+    <tableColumn name=" [Απόκτηση νέων δεξιοτήτων]" id="30"/>
+    <tableColumn name=" [Σύγχρονος εξοπλισμός]" id="31"/>
+    <tableColumn name=" [Επάρκεια υλικών]" id="32"/>
+    <tableColumn name=" [Καθαριότητα]" id="33"/>
+    <tableColumn name=" [Ασφάλεια]" id="34"/>
+    <tableColumn name=" [Οργάνωση χώρων]" id="35"/>
+    <tableColumn name=" [Διαθεσιμότητα μηχανημάτων]" id="36"/>
+    <tableColumn name=" [Φυσικοθεραπευτές]" id="37"/>
+    <tableColumn name=" [Ιατροί]" id="38"/>
+    <tableColumn name=" [Εργοθεραπευτές]" id="39"/>
+    <tableColumn name=" [Λογοθεραπευτές]" id="40"/>
+    <tableColumn name=" [Ψυχολόγοι]" id="41"/>
+    <tableColumn name=" [Κοινωνικοί λειτουργοί]" id="42"/>
+    <tableColumn name=" [Διοικητικό προσωπικό]" id="43"/>
+    <tableColumn name=" [Διαθεσιμότητα]" id="44"/>
+    <tableColumn name=" [Καθοδήγηση]" id="45"/>
+    <tableColumn name=" [Μεταδοτικότητα γνώσεων]" id="46"/>
+    <tableColumn name=" [Ανατροφοδότηση]" id="47"/>
+    <tableColumn name=" [Δικαιοσύνη]" id="48"/>
+    <tableColumn name=" [Υποστήριξη]" id="49"/>
+    <tableColumn name=" [Προσιτότητα]" id="50"/>
+    <tableColumn name=" [Ενδιαφέρον για τους φοιτητές]" id="51"/>
+    <tableColumn name=" [Ηγεσία]" id="52"/>
+    <tableColumn name=" [Οργάνωση]" id="53"/>
+    <tableColumn name=" [Επαγγελματισμός]" id="54"/>
+    <tableColumn name=" [Δημιουργία θετικού κλίματος]" id="55"/>
+    <tableColumn name=" [Ένιωσα μέλος της ομάδας.]" id="56"/>
+    <tableColumn name=" [Με αντιμετώπισαν με σεβασμό.]" id="57"/>
+    <tableColumn name=" [Μπορούσα να εκφράζω απορίες.]" id="58"/>
+    <tableColumn name=" [Ένιωθα ασφαλής να κάνω λάθος και να μάθω.]" id="59"/>
+    <tableColumn name=" [Η συνεργασία ήταν αποτελεσματική.]" id="60"/>
+    <tableColumn name=" [Χώρος εργασίας]" id="61"/>
+    <tableColumn name=" [Αποδυτήρια]" id="62"/>
+    <tableColumn name=" [Χώρος διαλείμματος]" id="63"/>
+    <tableColumn name=" [Υγιεινή]" id="64"/>
+    <tableColumn name=" [Ωράριο]" id="65"/>
+    <tableColumn name=" [Πρόσβαση σε εκπαιδευτικό υλικό]" id="66"/>
+    <tableColumn name="Πόσο πιθανό είναι να προτείνατε το Τμήμα Φυσικοθεραπείας του νοσοκομείου μας σε άλλους φοιτητές για την πραγματοποίηση της πρακτικής τους άσκησης; " id="67"/>
+    <tableColumn name="Ποια θεωρείτε ότι ήταν τα σημαντικότερα θετικά στοιχεία της πρακτικής σας άσκησης; " id="68"/>
+    <tableColumn name="Ποιοι τομείς χρειάζονται βελτίωση; " id="69"/>
+    <tableColumn name="Ποιες εκπαιδευτικές δραστηριότητες θα θέλατε να ενισχυθούν; " id="70"/>
+    <tableColumn name="Υπάρχουν δραστηριότητες που θα θέλατε να προστεθούν; " id="71"/>
+    <tableColumn name="Περιγράψτε μια εμπειρία που θεωρείτε ιδιαίτερα σημαντική κατά τη διάρκεια της πρακτικής σας. " id="72"/>
+    <tableColumn name="Επιπλέον σχόλια ή προτάσεις. " id="73"/>
   </tableColumns>
   <tableStyleInfo name="Form Responses 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" headerRowCount="1"/>
-    </ext>
-  </extLst>
 </table>
 </file>
 
@@ -918,6 +1051,1111 @@
         <v>72</v>
       </c>
     </row>
+    <row r="2" ht="22.5" customHeight="1">
+      <c r="A2" s="2">
+        <v>46238.81261105324</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AK2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AM2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AN2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AO2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AP2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AQ2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AR2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AS2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AT2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AU2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AV2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AX2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AY2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AZ2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="BA2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="BB2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="BC2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="BD2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="BE2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="BF2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="BG2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="BH2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="BI2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="BJ2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="BK2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="BL2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="BM2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="BN2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="BO2" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="BP2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="BQ2" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="BR2" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="BS2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="BT2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="BU2" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="4">
+        <v>46238.813880347225</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F3" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="U3" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AB3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AH3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AJ3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AK3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AP3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AQ3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AR3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AS3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AT3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AU3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AV3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AW3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AX3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AY3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AZ3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="BA3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="BB3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="BC3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="BD3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="BE3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="BF3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="BG3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="BH3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="BI3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="BJ3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="BK3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="BL3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="BM3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="BN3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="BO3" s="5">
+        <v>5.0</v>
+      </c>
+      <c r="BP3" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="BQ3" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="BR3" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="BS3" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="BT3" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="BU3" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="4">
+        <v>46238.81851320602</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="R4" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="S4" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="T4" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="U4" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z4" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA4" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AB4" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AC4" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AD4" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE4" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AF4" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AG4" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AH4" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AI4" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AJ4" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AK4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AM4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AN4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AO4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AP4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AQ4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AR4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AS4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AT4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AU4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AV4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AW4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AX4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AZ4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="BA4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="BC4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="BD4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="BE4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="BF4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="BG4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="BH4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="BI4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="BJ4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="BK4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="BL4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="BM4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="BN4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="BO4" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="BP4" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="BQ4" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="BR4" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="BS4" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="BT4" s="5">
+        <v>5.0</v>
+      </c>
+      <c r="BU4" s="5">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="5" ht="22.5" customHeight="1">
+      <c r="A5" s="4">
+        <v>46238.82189491898</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F5" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="I5" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="K5" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="R5" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="S5" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="T5" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="U5" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="V5" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="X5" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y5" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z5" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA5" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AB5" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC5" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD5" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE5" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF5" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG5" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AH5" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="AI5" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="AJ5" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="AK5" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL5" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM5" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="AN5" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AO5" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="AP5" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="AQ5" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="AR5" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="AS5" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AT5" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AU5" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="AV5" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW5" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="AX5" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY5" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AZ5" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="BA5" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="BB5" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="BC5" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="BD5" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="BE5" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="BF5" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="BG5" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="BH5" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="BI5" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="BJ5" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="BK5" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="BL5" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="BM5" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="BN5" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="BO5" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="BP5" s="5">
+        <v>7.0</v>
+      </c>
+      <c r="BQ5" s="5">
+        <v>5.0</v>
+      </c>
+      <c r="BR5" s="5">
+        <v>6.0</v>
+      </c>
+      <c r="BS5" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="BT5" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="BU5" s="5">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" customHeight="1">
+      <c r="A6" s="4">
+        <v>46238.82516872685</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="J6" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q6" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="R6" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="S6" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="T6" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="U6" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="V6" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="W6" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="X6" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y6" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z6" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA6" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AB6" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC6" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD6" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="AE6" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AF6" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AG6" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="AH6" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI6" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ6" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="AK6" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL6" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="AM6" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="AN6" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AO6" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AP6" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AQ6" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="AR6" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="AS6" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AT6" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="AU6" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AV6" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="AW6" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="AX6" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY6" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="AZ6" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="BA6" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="BB6" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="BC6" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="BD6" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="BE6" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="BF6" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="BG6" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="BH6" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="BI6" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="BJ6" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="BK6" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="BL6" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="BM6" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="BN6" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="BO6" s="5">
+        <v>7.0</v>
+      </c>
+      <c r="BP6" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="BQ6" s="5">
+        <v>9.0</v>
+      </c>
+      <c r="BR6" s="5">
+        <v>8.0</v>
+      </c>
+      <c r="BS6" s="5">
+        <v>7.0</v>
+      </c>
+      <c r="BT6" s="5">
+        <v>6.0</v>
+      </c>
+      <c r="BU6" s="5">
+        <v>5.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
   <tableParts count="1">
